--- a/data/dummy_univar.xlsx
+++ b/data/dummy_univar.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uq-my.sharepoint.com/personal/uqmkoh1_uq_edu_au/Documents/International Programs/R Crash Course/Int-Progs-R-Crash-Course/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="31" documentId="11_F25DC773A252ABDACC1048A619DA75925ADE58EB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5F39E421-D0F8-45AF-8787-D193FA1D131B}"/>
+  <xr:revisionPtr revIDLastSave="258" documentId="11_F25DC773A252ABDACC1048A619DA75925ADE58EB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{28DA631F-DE21-40C1-8E07-6D30D1637333}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="t test" sheetId="1" r:id="rId1"/>
     <sheet name="anova" sheetId="2" r:id="rId2"/>
     <sheet name="linear model" sheetId="3" r:id="rId3"/>
-    <sheet name="Chisq" sheetId="4" r:id="rId4"/>
+    <sheet name="Chisq Goodness of Fit" sheetId="4" r:id="rId4"/>
+    <sheet name="Chisq Test of Ind" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="29">
   <si>
     <t>location</t>
   </si>
@@ -51,6 +52,81 @@
   </si>
   <si>
     <t>Adams Beach</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adams Beach </t>
+  </si>
+  <si>
+    <t>polka Point</t>
+  </si>
+  <si>
+    <t>coral morphospecies</t>
+  </si>
+  <si>
+    <t>size_mm</t>
+  </si>
+  <si>
+    <t>Coral Gardens</t>
+  </si>
+  <si>
+    <t>Blue Pools</t>
+  </si>
+  <si>
+    <t>Branching</t>
+  </si>
+  <si>
+    <t>Soft</t>
+  </si>
+  <si>
+    <t>Massive</t>
+  </si>
+  <si>
+    <t>Heron Bommie</t>
+  </si>
+  <si>
+    <t>length_cm</t>
+  </si>
+  <si>
+    <t>girth_cm</t>
+  </si>
+  <si>
+    <t>Mangrove</t>
+  </si>
+  <si>
+    <t>Seagrass</t>
+  </si>
+  <si>
+    <t>Snapper</t>
+  </si>
+  <si>
+    <t>Whiting</t>
+  </si>
+  <si>
+    <t>Prawns</t>
+  </si>
+  <si>
+    <t>North</t>
+  </si>
+  <si>
+    <t>South</t>
+  </si>
+  <si>
+    <t xml:space="preserve">East </t>
+  </si>
+  <si>
+    <t>West</t>
+  </si>
+  <si>
+    <t>Stingrays</t>
+  </si>
+  <si>
+    <t>Habitat</t>
+  </si>
+  <si>
+    <t>Count</t>
+  </si>
+  <si>
+    <t>Species</t>
   </si>
 </sst>
 </file>
@@ -384,8 +460,7 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <f ca="1">RANDBETWEEN(1,716)</f>
-        <v>227</v>
+        <v>470</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
@@ -393,8 +468,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <f t="shared" ref="B3:B30" ca="1" si="0">RANDBETWEEN(1,716)</f>
-        <v>355</v>
+        <v>672</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
@@ -402,8 +476,7 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <f t="shared" ca="1" si="0"/>
-        <v>635</v>
+        <v>505</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
@@ -411,8 +484,7 @@
         <v>2</v>
       </c>
       <c r="B5">
-        <f t="shared" ca="1" si="0"/>
-        <v>505</v>
+        <v>576</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
@@ -420,8 +492,7 @@
         <v>2</v>
       </c>
       <c r="B6">
-        <f t="shared" ca="1" si="0"/>
-        <v>205</v>
+        <v>228</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
@@ -429,8 +500,7 @@
         <v>2</v>
       </c>
       <c r="B7">
-        <f t="shared" ca="1" si="0"/>
-        <v>50</v>
+        <v>191</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
@@ -438,8 +508,7 @@
         <v>2</v>
       </c>
       <c r="B8">
-        <f t="shared" ca="1" si="0"/>
-        <v>615</v>
+        <v>675</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
@@ -447,8 +516,7 @@
         <v>2</v>
       </c>
       <c r="B9">
-        <f t="shared" ca="1" si="0"/>
-        <v>455</v>
+        <v>182</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
@@ -456,8 +524,7 @@
         <v>2</v>
       </c>
       <c r="B10">
-        <f t="shared" ca="1" si="0"/>
-        <v>638</v>
+        <v>33</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
@@ -465,8 +532,7 @@
         <v>2</v>
       </c>
       <c r="B11">
-        <f t="shared" ca="1" si="0"/>
-        <v>186</v>
+        <v>533</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
@@ -474,8 +540,7 @@
         <v>2</v>
       </c>
       <c r="B12">
-        <f t="shared" ca="1" si="0"/>
-        <v>562</v>
+        <v>194</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
@@ -483,8 +548,7 @@
         <v>2</v>
       </c>
       <c r="B13">
-        <f t="shared" ca="1" si="0"/>
-        <v>581</v>
+        <v>416</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
@@ -492,17 +556,15 @@
         <v>2</v>
       </c>
       <c r="B14">
-        <f t="shared" ca="1" si="0"/>
-        <v>527</v>
+        <v>554</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B15">
-        <f t="shared" ca="1" si="0"/>
-        <v>351</v>
+        <v>443</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
@@ -510,8 +572,7 @@
         <v>3</v>
       </c>
       <c r="B16">
-        <f ca="1">RANDBETWEEN(1,462)</f>
-        <v>258</v>
+        <v>356</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
@@ -519,8 +580,7 @@
         <v>3</v>
       </c>
       <c r="B17">
-        <f t="shared" ref="B17:B30" ca="1" si="1">RANDBETWEEN(1,462)</f>
-        <v>96</v>
+        <v>158</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
@@ -528,8 +588,7 @@
         <v>3</v>
       </c>
       <c r="B18">
-        <f t="shared" ca="1" si="1"/>
-        <v>46</v>
+        <v>152</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
@@ -537,17 +596,15 @@
         <v>3</v>
       </c>
       <c r="B19">
-        <f t="shared" ca="1" si="1"/>
-        <v>262</v>
+        <v>341</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B20">
-        <f t="shared" ca="1" si="1"/>
-        <v>290</v>
+        <v>76</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
@@ -555,8 +612,7 @@
         <v>3</v>
       </c>
       <c r="B21">
-        <f t="shared" ca="1" si="1"/>
-        <v>82</v>
+        <v>325</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
@@ -564,8 +620,7 @@
         <v>3</v>
       </c>
       <c r="B22">
-        <f t="shared" ca="1" si="1"/>
-        <v>81</v>
+        <v>28</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
@@ -573,8 +628,7 @@
         <v>3</v>
       </c>
       <c r="B23">
-        <f t="shared" ca="1" si="1"/>
-        <v>40</v>
+        <v>256</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
@@ -582,8 +636,7 @@
         <v>3</v>
       </c>
       <c r="B24">
-        <f t="shared" ca="1" si="1"/>
-        <v>322</v>
+        <v>37</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
@@ -591,8 +644,7 @@
         <v>3</v>
       </c>
       <c r="B25">
-        <f t="shared" ca="1" si="1"/>
-        <v>180</v>
+        <v>261</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
@@ -600,8 +652,7 @@
         <v>3</v>
       </c>
       <c r="B26">
-        <f t="shared" ca="1" si="1"/>
-        <v>21</v>
+        <v>70</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
@@ -609,8 +660,7 @@
         <v>3</v>
       </c>
       <c r="B27">
-        <f t="shared" ca="1" si="1"/>
-        <v>380</v>
+        <v>336</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
@@ -618,8 +668,7 @@
         <v>3</v>
       </c>
       <c r="B28">
-        <f t="shared" ca="1" si="1"/>
-        <v>449</v>
+        <v>325</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.3">
@@ -627,8 +676,7 @@
         <v>3</v>
       </c>
       <c r="B29">
-        <f t="shared" ca="1" si="1"/>
-        <v>215</v>
+        <v>54</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.3">
@@ -636,8 +684,7 @@
         <v>3</v>
       </c>
       <c r="B30">
-        <f t="shared" ca="1" si="1"/>
-        <v>293</v>
+        <v>351</v>
       </c>
     </row>
   </sheetData>
@@ -647,27 +694,921 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED0045DE-5C63-49A6-AA27-4C100ACF1084}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:C46"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2">
+        <v>1246</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6">
+        <v>1717</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10">
+        <v>1462</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11" t="s">
+        <v>11</v>
+      </c>
+      <c r="C11">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12">
+        <v>2711</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" t="s">
+        <v>12</v>
+      </c>
+      <c r="C13">
+        <v>4175</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>12</v>
+      </c>
+      <c r="C14">
+        <v>4267</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" t="s">
+        <v>12</v>
+      </c>
+      <c r="C15">
+        <v>1374</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>13</v>
+      </c>
+      <c r="B16" t="s">
+        <v>12</v>
+      </c>
+      <c r="C16">
+        <v>2621</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>8</v>
+      </c>
+      <c r="B17" t="s">
+        <v>10</v>
+      </c>
+      <c r="C17">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>8</v>
+      </c>
+      <c r="B18" t="s">
+        <v>10</v>
+      </c>
+      <c r="C18">
+        <v>885</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>8</v>
+      </c>
+      <c r="B19" t="s">
+        <v>10</v>
+      </c>
+      <c r="C19">
+        <v>1491</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>8</v>
+      </c>
+      <c r="B20" t="s">
+        <v>10</v>
+      </c>
+      <c r="C20">
+        <v>951</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>8</v>
+      </c>
+      <c r="B21" t="s">
+        <v>10</v>
+      </c>
+      <c r="C21">
+        <v>2904</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>8</v>
+      </c>
+      <c r="B22" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>8</v>
+      </c>
+      <c r="B23" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>8</v>
+      </c>
+      <c r="B24" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>8</v>
+      </c>
+      <c r="B25" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>8</v>
+      </c>
+      <c r="B26" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26">
+        <v>885</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>8</v>
+      </c>
+      <c r="B27" t="s">
+        <v>12</v>
+      </c>
+      <c r="C27">
+        <v>4852</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>8</v>
+      </c>
+      <c r="B28" t="s">
+        <v>12</v>
+      </c>
+      <c r="C28">
+        <v>3389</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>8</v>
+      </c>
+      <c r="B29" t="s">
+        <v>12</v>
+      </c>
+      <c r="C29">
+        <v>1761</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>8</v>
+      </c>
+      <c r="B30" t="s">
+        <v>12</v>
+      </c>
+      <c r="C30">
+        <v>3739</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>8</v>
+      </c>
+      <c r="B31" t="s">
+        <v>12</v>
+      </c>
+      <c r="C31">
+        <v>4710</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>9</v>
+      </c>
+      <c r="B32" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>9</v>
+      </c>
+      <c r="B33" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33">
+        <v>4455</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>9</v>
+      </c>
+      <c r="B34" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34">
+        <v>1140</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>9</v>
+      </c>
+      <c r="B35" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35">
+        <v>1917</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>9</v>
+      </c>
+      <c r="B36" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>9</v>
+      </c>
+      <c r="B37" t="s">
+        <v>11</v>
+      </c>
+      <c r="C37">
+        <v>871</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>9</v>
+      </c>
+      <c r="B38" t="s">
+        <v>11</v>
+      </c>
+      <c r="C38">
+        <v>4005</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>9</v>
+      </c>
+      <c r="B39" t="s">
+        <v>11</v>
+      </c>
+      <c r="C39">
+        <v>2142</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>9</v>
+      </c>
+      <c r="B40" t="s">
+        <v>11</v>
+      </c>
+      <c r="C40">
+        <v>6820</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>9</v>
+      </c>
+      <c r="B41" t="s">
+        <v>11</v>
+      </c>
+      <c r="C41">
+        <v>6900</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>9</v>
+      </c>
+      <c r="B42" t="s">
+        <v>12</v>
+      </c>
+      <c r="C42">
+        <v>5058</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>9</v>
+      </c>
+      <c r="B43" t="s">
+        <v>12</v>
+      </c>
+      <c r="C43">
+        <v>8011</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>9</v>
+      </c>
+      <c r="B44" t="s">
+        <v>12</v>
+      </c>
+      <c r="C44">
+        <v>9173</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>9</v>
+      </c>
+      <c r="B45" t="s">
+        <v>12</v>
+      </c>
+      <c r="C45">
+        <v>9024</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>9</v>
+      </c>
+      <c r="B46" t="s">
+        <v>12</v>
+      </c>
+      <c r="C46">
+        <v>8371</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F51A396-00F2-42CF-B061-0404D60721A0}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>315.02</v>
+      </c>
+      <c r="B2">
+        <v>78.760000000000005</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>148.34</v>
+      </c>
+      <c r="B3">
+        <v>111.25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>81.7</v>
+      </c>
+      <c r="B4">
+        <v>61.28</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>92</v>
+      </c>
+      <c r="B5">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>129.35</v>
+      </c>
+      <c r="B6">
+        <v>97.01</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>78.63</v>
+      </c>
+      <c r="B7">
+        <v>58.97</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>328.6</v>
+      </c>
+      <c r="B8">
+        <v>82.15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>280.58999999999997</v>
+      </c>
+      <c r="B9">
+        <v>70.150000000000006</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>195.99</v>
+      </c>
+      <c r="B10">
+        <v>146.99</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>164.11</v>
+      </c>
+      <c r="B11">
+        <v>123.09</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>310.49</v>
+      </c>
+      <c r="B12">
+        <v>155.24</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>83.66</v>
+      </c>
+      <c r="B13">
+        <v>41.83</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <v>96.24</v>
+      </c>
+      <c r="B14">
+        <v>48.12</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <v>52.17</v>
+      </c>
+      <c r="B15">
+        <v>39.119999999999997</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>45.3</v>
+      </c>
+      <c r="B16">
+        <v>11.33</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <v>288.18</v>
+      </c>
+      <c r="B17">
+        <v>72.05</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18">
+        <v>102.1</v>
+      </c>
+      <c r="B18">
+        <v>76.58</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19">
+        <v>168.17</v>
+      </c>
+      <c r="B19">
+        <v>84.09</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20">
+        <v>129.69999999999999</v>
+      </c>
+      <c r="B20">
+        <v>32.43</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A21">
+        <v>203.49</v>
+      </c>
+      <c r="B21">
+        <v>152.62</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A22">
+        <v>30.36</v>
+      </c>
+      <c r="B22">
+        <v>15.18</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A23">
+        <v>133.94999999999999</v>
+      </c>
+      <c r="B23">
+        <v>33.49</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A24">
+        <v>254.52</v>
+      </c>
+      <c r="B24">
+        <v>127.26</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A25">
+        <v>183.06</v>
+      </c>
+      <c r="B25">
+        <v>91.53</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A26">
+        <v>319.16000000000003</v>
+      </c>
+      <c r="B26">
+        <v>239.37</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A27">
+        <v>57.78</v>
+      </c>
+      <c r="B27">
+        <v>14.45</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A28">
+        <v>263.62</v>
+      </c>
+      <c r="B28">
+        <v>131.81</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A29">
+        <v>303.47000000000003</v>
+      </c>
+      <c r="B29">
+        <v>151.74</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A30">
+        <v>240.29</v>
+      </c>
+      <c r="B30">
+        <v>120.15</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A31">
+        <v>180.76</v>
+      </c>
+      <c r="B31">
+        <v>45.19</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A61465A-5D7C-4AFF-9F52-6FF2AEFC0C6D}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>4</v>
+      </c>
+      <c r="B2">
+        <v>20</v>
+      </c>
+      <c r="C2">
+        <v>8</v>
+      </c>
+      <c r="D2">
+        <v>15</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DBE0446-1FC4-46AB-9357-90F102519A3E}">
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>